--- a/business_forms/014_internet_speed_survey_form--business_forms.xlsx
+++ b/business_forms/014_internet_speed_survey_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>internet_service_provider</t>
+          <t>internet_service_provider_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>internet service provider</t>
+          <t>Internet Service Provider 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>download_speed</t>
+          <t>download_speed_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>download speed</t>
+          <t>Download Speed 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>upload_speed</t>
+          <t>upload_speed_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>upload speed</t>
+          <t>Upload Speed 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -779,7 +779,7 @@
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="37" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
@@ -804,7 +804,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>internet_service_provider_choices</t>
+          <t>internet_service_provider_2_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -821,7 +821,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>internet_service_provider_choices</t>
+          <t>internet_service_provider_2_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -838,7 +838,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>download_speed_choices</t>
+          <t>download_speed_2_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -855,7 +855,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>download_speed_choices</t>
+          <t>download_speed_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -872,7 +872,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>upload_speed_choices</t>
+          <t>upload_speed_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -889,7 +889,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>upload_speed_choices</t>
+          <t>upload_speed_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
